--- a/output/casestudy_20260829.xlsx
+++ b/output/casestudy_20260829.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.21975419996306</v>
+        <v>20.63543540006503</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.05006799986586</v>
+        <v>20.97283899993636</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.60019010002725</v>
+        <v>12.51220509991981</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20.34284480009228</v>
+        <v>21.78320219996385</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21.95910410000943</v>
+        <v>24.78542199986987</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.00939960009418</v>
+        <v>15.17627399996854</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.2 초</t>
+          <t>20.6 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.1 초</t>
+          <t>21.0 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.3 초</t>
+          <t>21.8 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.0 초</t>
+          <t>24.8 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.0 초</t>
+          <t>15.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>111.0 초</t>
+          <t>117.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260829.xlsx
+++ b/output/casestudy_20260829.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20.63543540006503</v>
+        <v>19.2379946000874</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.97283899993636</v>
+        <v>19.85453750006855</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.51220509991981</v>
+        <v>11.62048189993948</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.78320219996385</v>
+        <v>20.31593040004373</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24.78542199986987</v>
+        <v>21.78663159999996</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.17627399996854</v>
+        <v>13.97771920007654</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.6 초</t>
+          <t>19.2 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.0 초</t>
+          <t>19.9 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>11.6 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.8 초</t>
+          <t>20.3 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.8 초</t>
+          <t>21.8 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.2 초</t>
+          <t>14.0 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>117.9 초</t>
+          <t>108.6 초</t>
         </is>
       </c>
     </row>
